--- a/artfynd/A 46259-2024 artfynd.xlsx
+++ b/artfynd/A 46259-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128482235</v>
       </c>
       <c r="B2" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>128482583</v>
       </c>
       <c r="B3" t="n">
-        <v>92057</v>
+        <v>92149</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -886,7 +886,7 @@
         <v>128482679</v>
       </c>
       <c r="B4" t="n">
-        <v>92295</v>
+        <v>92387</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -985,10 +985,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128482487</v>
+        <v>128483076</v>
       </c>
       <c r="B5" t="n">
-        <v>75156</v>
+        <v>91470</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -996,37 +996,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6440</v>
+        <v>5432</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Norra stugan, Norra stugan, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>408154</v>
+        <v>408199</v>
       </c>
       <c r="R5" t="n">
-        <v>7017305</v>
+        <v>7017224</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1067,7 +1064,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1091,10 +1087,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128483076</v>
+        <v>128482487</v>
       </c>
       <c r="B6" t="n">
-        <v>91378</v>
+        <v>75171</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1102,34 +1098,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>6440</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Norra stugan, Norra stugan, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>408199</v>
+        <v>408154</v>
       </c>
       <c r="R6" t="n">
-        <v>7017224</v>
+        <v>7017305</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1170,6 +1169,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1196,7 +1196,7 @@
         <v>128483078</v>
       </c>
       <c r="B7" t="n">
-        <v>88617</v>
+        <v>88709</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 46259-2024 artfynd.xlsx
+++ b/artfynd/A 46259-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128482235</v>
       </c>
       <c r="B2" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>128482583</v>
       </c>
       <c r="B3" t="n">
-        <v>92149</v>
+        <v>92155</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -886,7 +886,7 @@
         <v>128482679</v>
       </c>
       <c r="B4" t="n">
-        <v>92387</v>
+        <v>92393</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -988,7 +988,7 @@
         <v>128483076</v>
       </c>
       <c r="B5" t="n">
-        <v>91470</v>
+        <v>91476</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1090,7 +1090,7 @@
         <v>128482487</v>
       </c>
       <c r="B6" t="n">
-        <v>75171</v>
+        <v>75175</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1196,7 +1196,7 @@
         <v>128483078</v>
       </c>
       <c r="B7" t="n">
-        <v>88709</v>
+        <v>88715</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 46259-2024 artfynd.xlsx
+++ b/artfynd/A 46259-2024 artfynd.xlsx
@@ -784,7 +784,7 @@
         <v>128482583</v>
       </c>
       <c r="B3" t="n">
-        <v>92155</v>
+        <v>92161</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -886,7 +886,7 @@
         <v>128482679</v>
       </c>
       <c r="B4" t="n">
-        <v>92393</v>
+        <v>92399</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -985,10 +985,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128483076</v>
+        <v>128482487</v>
       </c>
       <c r="B5" t="n">
-        <v>91476</v>
+        <v>75175</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -996,34 +996,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>6440</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Norra stugan, Norra stugan, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>408199</v>
+        <v>408154</v>
       </c>
       <c r="R5" t="n">
-        <v>7017224</v>
+        <v>7017305</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1064,6 +1067,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1087,10 +1091,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128482487</v>
+        <v>128483076</v>
       </c>
       <c r="B6" t="n">
-        <v>75175</v>
+        <v>91482</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1098,37 +1102,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6440</v>
+        <v>5432</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Norra stugan, Norra stugan, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>408154</v>
+        <v>408199</v>
       </c>
       <c r="R6" t="n">
-        <v>7017305</v>
+        <v>7017224</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1169,7 +1170,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1196,7 +1196,7 @@
         <v>128483078</v>
       </c>
       <c r="B7" t="n">
-        <v>88715</v>
+        <v>88721</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 46259-2024 artfynd.xlsx
+++ b/artfynd/A 46259-2024 artfynd.xlsx
@@ -985,10 +985,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128482487</v>
+        <v>128483076</v>
       </c>
       <c r="B5" t="n">
-        <v>75175</v>
+        <v>91482</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -996,37 +996,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6440</v>
+        <v>5432</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Norra stugan, Norra stugan, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>408154</v>
+        <v>408199</v>
       </c>
       <c r="R5" t="n">
-        <v>7017305</v>
+        <v>7017224</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1067,7 +1064,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1091,10 +1087,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128483076</v>
+        <v>128482487</v>
       </c>
       <c r="B6" t="n">
-        <v>91482</v>
+        <v>75175</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1102,34 +1098,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>6440</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Norra stugan, Norra stugan, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>408199</v>
+        <v>408154</v>
       </c>
       <c r="R6" t="n">
-        <v>7017224</v>
+        <v>7017305</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1170,6 +1169,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 46259-2024 artfynd.xlsx
+++ b/artfynd/A 46259-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128482235</v>
       </c>
       <c r="B2" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>128482583</v>
       </c>
       <c r="B3" t="n">
-        <v>92161</v>
+        <v>92163</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -886,7 +886,7 @@
         <v>128482679</v>
       </c>
       <c r="B4" t="n">
-        <v>92399</v>
+        <v>92401</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -985,10 +985,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128483076</v>
+        <v>128482487</v>
       </c>
       <c r="B5" t="n">
-        <v>91482</v>
+        <v>75177</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -996,34 +996,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>6440</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Norra stugan, Norra stugan, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>408199</v>
+        <v>408154</v>
       </c>
       <c r="R5" t="n">
-        <v>7017224</v>
+        <v>7017305</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1064,6 +1067,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1087,10 +1091,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128482487</v>
+        <v>128483076</v>
       </c>
       <c r="B6" t="n">
-        <v>75175</v>
+        <v>91484</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1098,37 +1102,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6440</v>
+        <v>5432</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Norra stugan, Norra stugan, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>408154</v>
+        <v>408199</v>
       </c>
       <c r="R6" t="n">
-        <v>7017305</v>
+        <v>7017224</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1169,7 +1170,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1196,7 +1196,7 @@
         <v>128483078</v>
       </c>
       <c r="B7" t="n">
-        <v>88721</v>
+        <v>88723</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 46259-2024 artfynd.xlsx
+++ b/artfynd/A 46259-2024 artfynd.xlsx
@@ -985,10 +985,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128482487</v>
+        <v>128483076</v>
       </c>
       <c r="B5" t="n">
-        <v>75177</v>
+        <v>91484</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -996,37 +996,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6440</v>
+        <v>5432</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Norra stugan, Norra stugan, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>408154</v>
+        <v>408199</v>
       </c>
       <c r="R5" t="n">
-        <v>7017305</v>
+        <v>7017224</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1067,7 +1064,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1091,10 +1087,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128483076</v>
+        <v>128482487</v>
       </c>
       <c r="B6" t="n">
-        <v>91484</v>
+        <v>75177</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1102,34 +1098,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>6440</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Norra stugan, Norra stugan, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>408199</v>
+        <v>408154</v>
       </c>
       <c r="R6" t="n">
-        <v>7017224</v>
+        <v>7017305</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1170,6 +1169,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 46259-2024 artfynd.xlsx
+++ b/artfynd/A 46259-2024 artfynd.xlsx
@@ -784,7 +784,7 @@
         <v>128482583</v>
       </c>
       <c r="B3" t="n">
-        <v>92163</v>
+        <v>92164</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -886,7 +886,7 @@
         <v>128482679</v>
       </c>
       <c r="B4" t="n">
-        <v>92401</v>
+        <v>92402</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -988,7 +988,7 @@
         <v>128483076</v>
       </c>
       <c r="B5" t="n">
-        <v>91484</v>
+        <v>91485</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 46259-2024 artfynd.xlsx
+++ b/artfynd/A 46259-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128482235</v>
       </c>
       <c r="B2" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>128482583</v>
       </c>
       <c r="B3" t="n">
-        <v>92164</v>
+        <v>92191</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -886,7 +886,7 @@
         <v>128482679</v>
       </c>
       <c r="B4" t="n">
-        <v>92402</v>
+        <v>92429</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -988,7 +988,7 @@
         <v>128483076</v>
       </c>
       <c r="B5" t="n">
-        <v>91485</v>
+        <v>91512</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1090,7 +1090,7 @@
         <v>128482487</v>
       </c>
       <c r="B6" t="n">
-        <v>75177</v>
+        <v>75204</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1196,7 +1196,7 @@
         <v>128483078</v>
       </c>
       <c r="B7" t="n">
-        <v>88723</v>
+        <v>88750</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 46259-2024 artfynd.xlsx
+++ b/artfynd/A 46259-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128482235</v>
       </c>
       <c r="B2" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>128482583</v>
       </c>
       <c r="B3" t="n">
-        <v>92191</v>
+        <v>92196</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -886,7 +886,7 @@
         <v>128482679</v>
       </c>
       <c r="B4" t="n">
-        <v>92429</v>
+        <v>92434</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -988,7 +988,7 @@
         <v>128483076</v>
       </c>
       <c r="B5" t="n">
-        <v>91512</v>
+        <v>91517</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1090,7 +1090,7 @@
         <v>128482487</v>
       </c>
       <c r="B6" t="n">
-        <v>75204</v>
+        <v>75205</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1196,7 +1196,7 @@
         <v>128483078</v>
       </c>
       <c r="B7" t="n">
-        <v>88750</v>
+        <v>88754</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 46259-2024 artfynd.xlsx
+++ b/artfynd/A 46259-2024 artfynd.xlsx
@@ -784,7 +784,7 @@
         <v>128482583</v>
       </c>
       <c r="B3" t="n">
-        <v>92196</v>
+        <v>92201</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -886,7 +886,7 @@
         <v>128482679</v>
       </c>
       <c r="B4" t="n">
-        <v>92434</v>
+        <v>92439</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -988,7 +988,7 @@
         <v>128483076</v>
       </c>
       <c r="B5" t="n">
-        <v>91517</v>
+        <v>91522</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1196,7 +1196,7 @@
         <v>128483078</v>
       </c>
       <c r="B7" t="n">
-        <v>88754</v>
+        <v>88755</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 46259-2024 artfynd.xlsx
+++ b/artfynd/A 46259-2024 artfynd.xlsx
@@ -985,10 +985,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128483076</v>
+        <v>128482487</v>
       </c>
       <c r="B5" t="n">
-        <v>91522</v>
+        <v>75205</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -996,34 +996,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>6440</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Norra stugan, Norra stugan, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>408199</v>
+        <v>408154</v>
       </c>
       <c r="R5" t="n">
-        <v>7017224</v>
+        <v>7017305</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1064,6 +1067,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1087,10 +1091,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128482487</v>
+        <v>128483076</v>
       </c>
       <c r="B6" t="n">
-        <v>75205</v>
+        <v>91522</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1098,37 +1102,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6440</v>
+        <v>5432</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Norra stugan, Norra stugan, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>408154</v>
+        <v>408199</v>
       </c>
       <c r="R6" t="n">
-        <v>7017305</v>
+        <v>7017224</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1169,7 +1170,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 46259-2024 artfynd.xlsx
+++ b/artfynd/A 46259-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128482235</v>
       </c>
       <c r="B2" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>128482583</v>
       </c>
       <c r="B3" t="n">
-        <v>92201</v>
+        <v>92205</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -886,7 +886,7 @@
         <v>128482679</v>
       </c>
       <c r="B4" t="n">
-        <v>92439</v>
+        <v>92443</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -988,7 +988,7 @@
         <v>128482487</v>
       </c>
       <c r="B5" t="n">
-        <v>75205</v>
+        <v>75209</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1094,7 +1094,7 @@
         <v>128483076</v>
       </c>
       <c r="B6" t="n">
-        <v>91522</v>
+        <v>91526</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1196,7 +1196,7 @@
         <v>128483078</v>
       </c>
       <c r="B7" t="n">
-        <v>88755</v>
+        <v>88759</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 46259-2024 artfynd.xlsx
+++ b/artfynd/A 46259-2024 artfynd.xlsx
@@ -985,10 +985,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128482487</v>
+        <v>128483076</v>
       </c>
       <c r="B5" t="n">
-        <v>75209</v>
+        <v>91526</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -996,37 +996,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6440</v>
+        <v>5432</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Norra stugan, Norra stugan, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>408154</v>
+        <v>408199</v>
       </c>
       <c r="R5" t="n">
-        <v>7017305</v>
+        <v>7017224</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1067,7 +1064,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1091,10 +1087,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128483076</v>
+        <v>128482487</v>
       </c>
       <c r="B6" t="n">
-        <v>91526</v>
+        <v>75209</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1102,34 +1098,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>6440</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Norra stugan, Norra stugan, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>408199</v>
+        <v>408154</v>
       </c>
       <c r="R6" t="n">
-        <v>7017224</v>
+        <v>7017305</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1170,6 +1169,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 46259-2024 artfynd.xlsx
+++ b/artfynd/A 46259-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128482235</v>
       </c>
       <c r="B2" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>128482583</v>
       </c>
       <c r="B3" t="n">
-        <v>92205</v>
+        <v>92210</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -886,7 +886,7 @@
         <v>128482679</v>
       </c>
       <c r="B4" t="n">
-        <v>92443</v>
+        <v>92448</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -985,10 +985,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128483076</v>
+        <v>128482487</v>
       </c>
       <c r="B5" t="n">
-        <v>91526</v>
+        <v>83005</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -996,34 +996,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>6440</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Norra stugan, Norra stugan, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>408199</v>
+        <v>408154</v>
       </c>
       <c r="R5" t="n">
-        <v>7017224</v>
+        <v>7017305</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1064,6 +1067,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1087,10 +1091,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128482487</v>
+        <v>128483076</v>
       </c>
       <c r="B6" t="n">
-        <v>75209</v>
+        <v>91531</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1098,37 +1102,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6440</v>
+        <v>5432</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Norra stugan, Norra stugan, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>408154</v>
+        <v>408199</v>
       </c>
       <c r="R6" t="n">
-        <v>7017305</v>
+        <v>7017224</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1169,7 +1170,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1196,7 +1196,7 @@
         <v>128483078</v>
       </c>
       <c r="B7" t="n">
-        <v>88759</v>
+        <v>88764</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 46259-2024 artfynd.xlsx
+++ b/artfynd/A 46259-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,48 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128482235</v>
+        <v>128482583</v>
       </c>
       <c r="B2" t="n">
-        <v>79029</v>
+        <v>92632</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Norra stugan, Norra stugan, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>408166</v>
+        <v>408172</v>
       </c>
       <c r="R2" t="n">
-        <v>7017301</v>
+        <v>7017349</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -757,7 +754,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -781,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128482583</v>
+        <v>128483078</v>
       </c>
       <c r="B3" t="n">
-        <v>92213</v>
+        <v>89143</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -792,21 +788,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>3298</v>
+        <v>4405</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Diskvaxskivling</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Hygrophorus discoideus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Pers.) Fr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -816,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>408172</v>
+        <v>408199</v>
       </c>
       <c r="R3" t="n">
-        <v>7017349</v>
+        <v>7017224</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -886,7 +882,7 @@
         <v>128482679</v>
       </c>
       <c r="B4" t="n">
-        <v>92451</v>
+        <v>92869</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -985,45 +981,48 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128483076</v>
+        <v>128482235</v>
       </c>
       <c r="B5" t="n">
-        <v>91533</v>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Norra stugan, Norra stugan, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>408199</v>
+        <v>408166</v>
       </c>
       <c r="R5" t="n">
-        <v>7017224</v>
+        <v>7017301</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1064,6 +1063,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1090,7 +1090,7 @@
         <v>128482487</v>
       </c>
       <c r="B6" t="n">
-        <v>83005</v>
+        <v>83307</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1191,108 +1191,6 @@
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>128483078</v>
-      </c>
-      <c r="B7" t="n">
-        <v>88766</v>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>4405</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Diskvaxskivling</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>Hygrophorus discoideus</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>(Pers.) Fr.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>Norra stugan, Norra stugan, Jmt</t>
-        </is>
-      </c>
-      <c r="Q7" t="n">
-        <v>408199</v>
-      </c>
-      <c r="R7" t="n">
-        <v>7017224</v>
-      </c>
-      <c r="S7" t="n">
-        <v>10</v>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>Åre</t>
-        </is>
-      </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>Undersåker</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>2025-09-16</t>
-        </is>
-      </c>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>2025-09-16</t>
-        </is>
-      </c>
-      <c r="AD7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>Lövrik gransumpskog/naturskog</t>
-        </is>
-      </c>
-      <c r="AT7" t="inlineStr"/>
-      <c r="AW7" t="inlineStr">
-        <is>
-          <t>Rashid Kadhim</t>
-        </is>
-      </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>Rashid Kadhim</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 46259-2024 artfynd.xlsx
+++ b/artfynd/A 46259-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128482583</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -876,6 +886,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128483078</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -978,6 +993,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128482679</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1084,6 +1104,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128482235</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1190,8 +1215,20 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128482487</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>